--- a/questionnaire_templates/050_wealth_preservation_assessment--questionnaire_templates.xlsx
+++ b/questionnaire_templates/050_wealth_preservation_assessment--questionnaire_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1083,8 +1083,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
-    <col width="50" customWidth="1" min="2" max="2"/>
-    <col width="50" customWidth="1" min="3" max="3"/>
+    <col width="25" customWidth="1" min="2" max="2"/>
+    <col width="25" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'cash'}</t>
+          <t>cash</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Cash'}</t>
+          <t>Cash</t>
         </is>
       </c>
     </row>
@@ -1129,12 +1129,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'stocks'}</t>
+          <t>stocks</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Stocks'}</t>
+          <t>Stocks</t>
         </is>
       </c>
     </row>
@@ -1146,12 +1146,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'bonds'}</t>
+          <t>bonds</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Bonds'}</t>
+          <t>Bonds</t>
         </is>
       </c>
     </row>
@@ -1163,12 +1163,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'alternative_investments'}</t>
+          <t>alternative_investments</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Alternative Investments'}</t>
+          <t>Alternative Investments</t>
         </is>
       </c>
     </row>
@@ -1180,12 +1180,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'retirement'}</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Retirement'}</t>
+          <t>Retirement</t>
         </is>
       </c>
     </row>
@@ -1197,12 +1197,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'wealth_creation'}</t>
+          <t>wealth_creation</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Wealth Creation'}</t>
+          <t>Wealth Creation</t>
         </is>
       </c>
     </row>
@@ -1214,12 +1214,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'debt_reduction'}</t>
+          <t>debt_reduction</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Debt Reduction'}</t>
+          <t>Debt Reduction</t>
         </is>
       </c>
     </row>
@@ -1231,12 +1231,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'salary'}</t>
+          <t>salary</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Salary'}</t>
+          <t>Salary</t>
         </is>
       </c>
     </row>
@@ -1248,12 +1248,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'investments'}</t>
+          <t>investments</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Investments'}</t>
+          <t>Investments</t>
         </is>
       </c>
     </row>
@@ -1265,12 +1265,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'rental_income'}</t>
+          <t>rental_income</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Rental Income'}</t>
+          <t>Rental Income</t>
         </is>
       </c>
     </row>
@@ -1282,12 +1282,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_'single'}</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 'Single'}</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_'joint'}</t>
+          <t>joint</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 'Joint'}</t>
+          <t>Joint</t>
         </is>
       </c>
     </row>
@@ -1316,12 +1316,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_'married'}</t>
+          <t>married</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 'Married'}</t>
+          <t>Married</t>
         </is>
       </c>
     </row>
@@ -1333,12 +1333,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_'short_term'}</t>
+          <t>short_term</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 'Short Term'}</t>
+          <t>Short Term</t>
         </is>
       </c>
     </row>
@@ -1350,12 +1350,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_'medium_term'}</t>
+          <t>medium_term</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 'Medium Term'}</t>
+          <t>Medium Term</t>
         </is>
       </c>
     </row>
@@ -1367,12 +1367,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_'long_term'}</t>
+          <t>long_term</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 'Long Term'}</t>
+          <t>Long Term</t>
         </is>
       </c>
     </row>
@@ -1384,12 +1384,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1401,12 +1401,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_12,_'name':_'estate_planning',_'label':_'estate_planning',_'hint':_none,_'type':_'select_one',_'options':_[{'value':_true},_{'value':_false}]}</t>
+          <t>estate_planning</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 12, 'name': 'estate_planning', 'label': 'Estate Planning', 'hint': None, 'type': 'select_one', 'options': [{'value': True}, {'value': False}]}</t>
+          <t>Estate Planning</t>
         </is>
       </c>
     </row>
@@ -1435,12 +1435,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1452,12 +1452,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1469,12 +1469,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1486,12 +1486,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1503,12 +1503,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1520,12 +1520,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1537,12 +1537,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1554,12 +1554,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1571,12 +1571,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1588,12 +1588,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1605,12 +1605,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_'primary_caregiver'}</t>
+          <t>primary_caregiver</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 'Primary Caregiver'}</t>
+          <t>Primary Caregiver</t>
         </is>
       </c>
     </row>
@@ -1622,12 +1622,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_'spouse'}</t>
+          <t>spouse</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 'Spouse'}</t>
+          <t>Spouse</t>
         </is>
       </c>
     </row>
@@ -1639,12 +1639,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_'child'}</t>
+          <t>child</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 'Child'}</t>
+          <t>Child</t>
         </is>
       </c>
     </row>
@@ -1656,12 +1656,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1673,12 +1673,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
@@ -1690,12 +1690,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1707,12 +1707,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
